--- a/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
@@ -105,54 +105,54 @@
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
-    <t xml:space="preserve">San Pedro</t>
+    <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maipú</t>
   </si>
   <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
     <t xml:space="preserve">Talagante</t>
   </si>
   <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>206.82</v>
+        <v>220.45</v>
       </c>
     </row>
     <row r="3">
@@ -651,7 +651,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>169.88</v>
+        <v>184.07</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>161.19</v>
+        <v>174.18</v>
       </c>
     </row>
     <row r="5">
@@ -685,7 +685,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>156.27</v>
+        <v>166.81</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>143.01</v>
+        <v>155.95</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>135.65</v>
+        <v>145.32</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>133.29</v>
+        <v>142.37</v>
       </c>
     </row>
     <row r="9">
@@ -753,7 +753,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>131.12</v>
+        <v>140.2</v>
       </c>
     </row>
     <row r="10">
@@ -770,7 +770,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>123.54</v>
+        <v>132.92</v>
       </c>
     </row>
     <row r="11">
@@ -787,7 +787,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>122.86</v>
+        <v>132.13</v>
       </c>
     </row>
     <row r="12">
@@ -804,7 +804,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>120.99</v>
+        <v>129.52</v>
       </c>
     </row>
     <row r="13">
@@ -821,7 +821,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>114.56</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="14">
@@ -838,7 +838,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>113.91</v>
+        <v>122.38</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>113.64</v>
+        <v>121.65</v>
       </c>
     </row>
     <row r="16">
@@ -872,7 +872,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>113.54</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="17">
@@ -883,13 +883,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13126</v>
+        <v>13111</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>110.34</v>
+        <v>117.92</v>
       </c>
     </row>
     <row r="18">
@@ -900,13 +900,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13111</v>
+        <v>13126</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>110.29</v>
+        <v>117.57</v>
       </c>
     </row>
     <row r="19">
@@ -923,7 +923,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>108.32</v>
+        <v>115.23</v>
       </c>
     </row>
     <row r="20">
@@ -940,7 +940,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>106.35</v>
+        <v>113.42</v>
       </c>
     </row>
     <row r="21">
@@ -957,7 +957,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>104.7</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="22">
@@ -974,7 +974,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>103.04</v>
+        <v>109.81</v>
       </c>
     </row>
     <row r="23">
@@ -991,7 +991,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>102.19</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="24">
@@ -1008,7 +1008,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>101.15</v>
+        <v>107.67</v>
       </c>
     </row>
     <row r="25">
@@ -1019,13 +1019,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13102</v>
+        <v>13505</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>99.78</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="26">
@@ -1036,13 +1036,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13505</v>
+        <v>13102</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>99.22</v>
+        <v>106.71</v>
       </c>
     </row>
     <row r="27">
@@ -1053,13 +1053,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13106</v>
+        <v>13103</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>99.04</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
@@ -1070,13 +1070,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13103</v>
+        <v>13106</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>98.99</v>
+        <v>104.85</v>
       </c>
     </row>
     <row r="29">
@@ -1093,7 +1093,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>96.39</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="30">
@@ -1104,13 +1104,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13101</v>
+        <v>13503</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>94.01</v>
+        <v>100.66</v>
       </c>
     </row>
     <row r="31">
@@ -1121,13 +1121,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>13503</v>
+        <v>13101</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>94</v>
+        <v>99.09</v>
       </c>
     </row>
     <row r="32">
@@ -1144,7 +1144,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>90.85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
@@ -1155,13 +1155,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13108</v>
+        <v>13501</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>89.63</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="34">
@@ -1172,13 +1172,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13501</v>
+        <v>13108</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>89.18</v>
+        <v>94.87</v>
       </c>
     </row>
     <row r="35">
@@ -1195,7 +1195,7 @@
         <v>2020</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>85.94</v>
+        <v>91.97</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1212,7 @@
         <v>2020</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>85.07</v>
+        <v>91.43</v>
       </c>
     </row>
     <row r="37">
@@ -1223,13 +1223,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>13303</v>
+        <v>13605</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>80.65</v>
+        <v>86.79</v>
       </c>
     </row>
     <row r="38">
@@ -1240,13 +1240,13 @@
         <v>42</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>13605</v>
+        <v>13128</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>80.62</v>
+        <v>85.82</v>
       </c>
     </row>
     <row r="39">
@@ -1257,13 +1257,13 @@
         <v>43</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>13128</v>
+        <v>13124</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>80.16</v>
+        <v>85.57</v>
       </c>
     </row>
     <row r="40">
@@ -1274,13 +1274,13 @@
         <v>44</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>13124</v>
+        <v>13303</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>79.48</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="41">
@@ -1297,7 +1297,7 @@
         <v>2020</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>79.01</v>
+        <v>84.27</v>
       </c>
     </row>
     <row r="42">
@@ -1314,7 +1314,7 @@
         <v>2020</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>77.74</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="43">
@@ -1331,7 +1331,7 @@
         <v>2020</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>76.78</v>
+        <v>82.58</v>
       </c>
     </row>
     <row r="44">
@@ -1348,7 +1348,7 @@
         <v>2020</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>76.72</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="45">
@@ -1365,7 +1365,7 @@
         <v>2020</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>76</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="46">
@@ -1382,7 +1382,7 @@
         <v>2020</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>73.48</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="47">
@@ -1399,7 +1399,7 @@
         <v>2020</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>69.95</v>
+        <v>76.32</v>
       </c>
     </row>
     <row r="48">
@@ -1416,7 +1416,7 @@
         <v>2020</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>67.35</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="49">
@@ -1433,7 +1433,7 @@
         <v>2020</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>67.35</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="50">
@@ -1450,7 +1450,7 @@
         <v>2020</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>65.86</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="51">
@@ -1467,7 +1467,7 @@
         <v>2020</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>52.64</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="52">
@@ -1484,7 +1484,7 @@
         <v>2020</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>44.68</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="53">
@@ -1501,7 +1501,7 @@
         <v>2020</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>40.13</v>
+        <v>42.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:15</t>
+    <t xml:space="preserve">2026-10-05 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
